--- a/CKA_2024.xlsx
+++ b/CKA_2024.xlsx
@@ -1,71 +1,335 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rcyber-my.sharepoint.com/personal/pritam_c_royalcyber_com/Documents/Desktop/Projects/DevOps/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0D47957-D094-46A5-8D93-285FFCFB2F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F7C3BD2-DA5C-4EE4-80BC-BA2ABC66F88F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Sheet2" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="49">
   <si>
     <t>CKA 2024</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Day (Folder)</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>Why it matters for AI product work</t>
+  </si>
+  <si>
+    <r>
+      <t>Status</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Day01</t>
+    </r>
+  </si>
+  <si>
+    <t>Docker fundamentals</t>
+  </si>
+  <si>
+    <t>Build the container that will run your FastAPI / inference service</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Day02</t>
+    </r>
+  </si>
+  <si>
+    <t>Dockerize a project</t>
+  </si>
+  <si>
+    <t>Turn your code into a reproducible image</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Day03</t>
+    </r>
+  </si>
+  <si>
+    <t>Multi‑stage Docker builds</t>
+  </si>
+  <si>
+    <t>Create small, production‑grade images (important for fast deploys)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Day05</t>
+    </r>
+  </si>
+  <si>
+    <t>Kubernetes architecture (conceptual)</t>
+  </si>
+  <si>
+    <t>Know the control‑plane components if you ever need to read logs or debug a pod</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Day07</t>
+    </r>
+  </si>
+  <si>
+    <t>Pods</t>
+  </si>
+  <si>
+    <t>Core unit of execution; you’ll understand pod specs when you view a deployment on a managed platform</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Day08</t>
+    </r>
+  </si>
+  <si>
+    <t>Deployments + rollback</t>
+  </si>
+  <si>
+    <t>Deploy your API and roll back if a new version breaks</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Day09</t>
+    </r>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>Expose your pods internally and understand ClusterIP / LoadBalancer basics</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Day10</t>
+    </r>
+  </si>
+  <si>
+    <t>Namespaces</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Separate </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <color rgb="FFCCCCCC"/>
+      </rPr>
+      <t>dev</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFCCCCCC"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <color rgb="FFCCCCCC"/>
+      </rPr>
+      <t>staging</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFCCCCCC"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <color rgb="FFCCCCCC"/>
+      </rPr>
+      <t>prod</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFCCCCCC"/>
+      </rPr>
+      <t xml:space="preserve"> environments cleanly</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Day16</t>
+    </r>
+  </si>
+  <si>
+    <t>Resource requests &amp; limits</t>
+  </si>
+  <si>
+    <t>Prevent a pod from starving others and avoid OOM kills (especially when you later add a GPU)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Day18</t>
+    </r>
+  </si>
+  <si>
+    <t>Probes (liveness, readiness, startup)</t>
+  </si>
+  <si>
+    <t>Ensure your inference API reports healthy before traffic reaches it</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Day19</t>
+    </r>
+  </si>
+  <si>
+    <t>ConfigMaps + Secrets</t>
+  </si>
+  <si>
+    <t>Store API keys, model IDs, and configuration without hard‑coding them</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Day33</t>
+    </r>
+  </si>
+  <si>
+    <t>Ingress</t>
+  </si>
+  <si>
+    <t>Expose your service to the internet (or use a managed ingress on Cloud Run)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Day36</t>
+    </r>
+  </si>
+  <si>
+    <t>Monitoring + logging</t>
+  </si>
+  <si>
+    <t>Observe latency, errors, and cost – essential for production AI services</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Resources/Helm</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFCCCCCC"/>
+      </rPr>
+      <t xml:space="preserve"> (read the Helm/readme.md)</t>
+    </r>
+  </si>
+  <si>
+    <t>Helm basics</t>
+  </si>
+  <si>
+    <t>One‑command install of tools like Prometheus, Grafana, or a DB chart when you do move to K8s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FFCCCCCC"/>
+      <family val="2"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFCCCCCC"/>
+      <family val="2"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF181818"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -73,12 +337,156 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -113,10 +521,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="1" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AF6EBA4-DD4A-FDFE-D430-3811B1DB0CB0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -125,15 +533,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1219200" y="762000"/>
-          <a:ext cx="7868748" cy="5039428"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -461,9 +869,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{050BC923-3203-4AD3-8FB0-B28411E6B576}">
-  <dimension ref="E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="E3:E3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E3" t="s">
@@ -474,4 +882,265 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
+    <col min="4" max="4" width="42.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="100.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" ht="86.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="114.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="143.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="186" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="100.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" ht="171.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="100.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" ht="171.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" ht="129" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" ht="129" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" ht="143.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" ht="143.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" ht="171" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>14</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>